--- a/data/dividends_info_20260601.xlsx
+++ b/data/dividends_info_20260601.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>58.91999816894531</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1527494955820211</v>
+        <v>0.1517706596254945</v>
       </c>
       <c r="J2" t="n">
         <v>287</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.34999847412109</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.287948518219935</v>
+        <v>1.275045501902276</v>
       </c>
       <c r="J3" t="n">
         <v>266</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J4" t="n">
         <v>196</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>58.90999984741211</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1527754205281222</v>
+        <v>0.1517706596254945</v>
       </c>
       <c r="J6" t="n">
         <v>196</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>175</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.7450008392334</v>
+        <v>23.02000045776367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.18707403841582</v>
+        <v>1.172893113079589</v>
       </c>
       <c r="J8" t="n">
         <v>175</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.179999828338623</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9652509972386709</v>
+        <v>0.8710801741070435</v>
       </c>
       <c r="J12" t="n">
         <v>126</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.949999809265137</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J13" t="n">
         <v>119</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.7450008392334</v>
+        <v>23.02000045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.18707403841582</v>
+        <v>1.172893113079589</v>
       </c>
       <c r="J14" t="n">
         <v>112</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>58.90999984741211</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1527754205281222</v>
+        <v>0.1517706596254945</v>
       </c>
       <c r="J15" t="n">
         <v>112</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J16" t="n">
         <v>105</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.949999809265137</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J18" t="n">
         <v>63</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.840000152587891</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="I19" t="n">
-        <v>4.280821805958635</v>
+        <v>4.258943864974011</v>
       </c>
       <c r="J19" t="n">
         <v>56</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.630000114440918</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>3.023758024613036</v>
+        <v>3.083700466439172</v>
       </c>
       <c r="J20" t="n">
         <v>49</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.61400032043457</v>
+        <v>9.560000419616699</v>
       </c>
       <c r="I21" t="n">
-        <v>2.704389341940936</v>
+        <v>2.719665152592373</v>
       </c>
       <c r="J21" t="n">
         <v>49</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.96000003814697</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="I22" t="n">
-        <v>4.010695176938778</v>
+        <v>4.037685153851224</v>
       </c>
       <c r="J22" t="n">
         <v>49</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.717999935150146</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="I23" t="n">
-        <v>5.917159866521503</v>
+        <v>5.91397844913971</v>
       </c>
       <c r="J23" t="n">
         <v>49</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.264999866485596</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>3.830806147081852</v>
+        <v>3.902438963875515</v>
       </c>
       <c r="J25" t="n">
         <v>49</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.95000076293945</v>
+        <v>18.45000076293945</v>
       </c>
       <c r="I26" t="n">
-        <v>1.984168785551417</v>
+        <v>2.037940295131433</v>
       </c>
       <c r="J26" t="n">
         <v>49</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>42</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.180000066757202</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I30" t="n">
-        <v>3.899082449407415</v>
+        <v>3.935185028814982</v>
       </c>
       <c r="J30" t="n">
         <v>35</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.570000171661377</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I31" t="n">
-        <v>1.53172860767207</v>
+        <v>1.594533078107776</v>
       </c>
       <c r="J31" t="n">
         <v>35</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.45000076293945</v>
+        <v>32.79999923706055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4484304830455813</v>
+        <v>0.4573170838080867</v>
       </c>
       <c r="J32" t="n">
         <v>35</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.63999938964844</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I34" t="n">
-        <v>4.196113187327925</v>
+        <v>4.260089831847112</v>
       </c>
       <c r="J34" t="n">
         <v>21</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.39999961853027</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6210191158248405</v>
+        <v>0.6260032179390458</v>
       </c>
       <c r="J35" t="n">
         <v>21</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.914999961853027</v>
+        <v>1.884999990463257</v>
       </c>
       <c r="I36" t="n">
-        <v>1.723237632238276</v>
+        <v>1.75066313883057</v>
       </c>
       <c r="J36" t="n">
         <v>21</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.324999809265137</v>
+        <v>5.224999904632568</v>
       </c>
       <c r="I37" t="n">
-        <v>5.446009584740636</v>
+        <v>5.550239335753506</v>
       </c>
       <c r="J37" t="n">
         <v>21</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.839999914169312</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I38" t="n">
-        <v>4.166666759798926</v>
+        <v>4.210526368624617</v>
       </c>
       <c r="J38" t="n">
         <v>21</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.665999889373779</v>
+        <v>2.651999950408936</v>
       </c>
       <c r="I39" t="n">
-        <v>5.198799915650257</v>
+        <v>5.226244441619541</v>
       </c>
       <c r="J39" t="n">
         <v>21</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53.36999893188477</v>
+        <v>52.47000122070312</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1804384721912</v>
+        <v>1.200686078412784</v>
       </c>
       <c r="J40" t="n">
         <v>21</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.639999866485596</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I41" t="n">
-        <v>2.482269562308288</v>
+        <v>2.456140433065195</v>
       </c>
       <c r="J41" t="n">
         <v>21</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.59000015258789</v>
+        <v>25.57999992370605</v>
       </c>
       <c r="I43" t="n">
-        <v>3.321609984101701</v>
+        <v>3.322908532193816</v>
       </c>
       <c r="J43" t="n">
         <v>21</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>58.90999984741211</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1527754205281222</v>
+        <v>0.1517706596254945</v>
       </c>
       <c r="J44" t="n">
         <v>21</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.460000038146973</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6849314889533817</v>
+        <v>0.6622516598117378</v>
       </c>
       <c r="J45" t="n">
         <v>21</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.193999767303467</v>
+        <v>6.188000202178955</v>
       </c>
       <c r="I46" t="n">
-        <v>2.927026264305596</v>
+        <v>2.929864157666956</v>
       </c>
       <c r="J46" t="n">
         <v>21</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.010000228881836</v>
+        <v>8.920000076293945</v>
       </c>
       <c r="I47" t="n">
-        <v>2.885682501611508</v>
+        <v>2.914798181347371</v>
       </c>
       <c r="J47" t="n">
         <v>21</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.734000205993652</v>
+        <v>9.704000473022461</v>
       </c>
       <c r="I48" t="n">
-        <v>2.845695440086789</v>
+        <v>2.854492853437837</v>
       </c>
       <c r="J48" t="n">
         <v>21</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.049999952316284</v>
+        <v>1.065000057220459</v>
       </c>
       <c r="I49" t="n">
-        <v>1.285714344102512</v>
+        <v>1.26760556569674</v>
       </c>
       <c r="J49" t="n">
         <v>14</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.01200008392334</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>3.652058331177646</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="J50" t="n">
         <v>14</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.240000009536743</v>
+        <v>3.244999885559082</v>
       </c>
       <c r="I52" t="n">
-        <v>4.93827159040277</v>
+        <v>4.93066273167013</v>
       </c>
       <c r="J52" t="n">
         <v>7</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.875</v>
       </c>
       <c r="I53" t="n">
-        <v>2.777777851363761</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J53" t="n">
         <v>7</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>28.89999961853027</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>3.840830500524587</v>
+        <v>3.874345601324452</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8820000290870667</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I55" t="n">
-        <v>3.401360432045807</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.5019999742507935</v>
+        <v>0.4995000064373016</v>
       </c>
       <c r="I56" t="n">
-        <v>4.58167354178179</v>
+        <v>4.604604545262806</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.539999961853027</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="I58" t="n">
-        <v>2.096436067083091</v>
+        <v>2.141327588143398</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.8100004196167</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="I61" t="n">
-        <v>1.581277630390228</v>
+        <v>1.584283930484756</v>
       </c>
       <c r="J61" t="n">
         <v>-7</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.849999904632568</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.7832898328355801</v>
       </c>
       <c r="J62" t="n">
         <v>-7</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.130000114440918</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I63" t="n">
-        <v>3.631961158439475</v>
+        <v>3.62318852264441</v>
       </c>
       <c r="J63" t="n">
         <v>-7</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.94999980926514</v>
+        <v>13</v>
       </c>
       <c r="I64" t="n">
-        <v>4.478764544730235</v>
+        <v>4.461538461538462</v>
       </c>
       <c r="J64" t="n">
         <v>-7</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.246999979019165</v>
+        <v>2.232000112533569</v>
       </c>
       <c r="I65" t="n">
-        <v>4.62839345665668</v>
+        <v>4.659497972961497</v>
       </c>
       <c r="J65" t="n">
         <v>-14</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11.01000022888184</v>
+        <v>10.91499996185303</v>
       </c>
       <c r="I66" t="n">
-        <v>2.633969064226369</v>
+        <v>2.656894191603524</v>
       </c>
       <c r="J66" t="n">
         <v>-14</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.085000038146973</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I67" t="n">
-        <v>3.693045495981532</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J67" t="n">
         <v>-14</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.43999862670898</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="I68" t="n">
-        <v>4.266389330358848</v>
+        <v>4.270833163625671</v>
       </c>
       <c r="J68" t="n">
         <v>-14</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>34.54999923706055</v>
+        <v>34.70999908447266</v>
       </c>
       <c r="I69" t="n">
-        <v>5.78871213940483</v>
+        <v>5.762028385920327</v>
       </c>
       <c r="J69" t="n">
         <v>-14</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.349999904632568</v>
+        <v>3.24399995803833</v>
       </c>
       <c r="I70" t="n">
-        <v>2.985074711844451</v>
+        <v>3.082614096594216</v>
       </c>
       <c r="J70" t="n">
         <v>-14</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>41.41999816894531</v>
+        <v>39.43000030517578</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3584258970617436</v>
+        <v>0.3765153407328592</v>
       </c>
       <c r="J71" t="n">
         <v>-14</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19.94000053405762</v>
+        <v>19.73999977111816</v>
       </c>
       <c r="I72" t="n">
-        <v>4.613841401000143</v>
+        <v>4.66058769334974</v>
       </c>
       <c r="J72" t="n">
         <v>-14</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.72000026702881</v>
+        <v>11.48999977111816</v>
       </c>
       <c r="I73" t="n">
-        <v>2.559726904136448</v>
+        <v>2.610966109451934</v>
       </c>
       <c r="J73" t="n">
         <v>-14</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>83.77999877929688</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="I74" t="n">
-        <v>1.241346401471896</v>
+        <v>1.263055679201458</v>
       </c>
       <c r="J74" t="n">
         <v>-14</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>46.04999923706055</v>
+        <v>45.2599983215332</v>
       </c>
       <c r="I75" t="n">
-        <v>1.520086887290646</v>
+        <v>1.546619588951605</v>
       </c>
       <c r="J75" t="n">
         <v>-14</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>54.34999847412109</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>4.047838200119797</v>
+        <v>4.00728586312144</v>
       </c>
       <c r="J76" t="n">
         <v>-14</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.197999954223633</v>
+        <v>9.095999717712402</v>
       </c>
       <c r="I77" t="n">
-        <v>9.349858711459291</v>
+        <v>9.454705658415364</v>
       </c>
       <c r="J77" t="n">
         <v>-14</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.72399997711182</v>
+        <v>11.6540002822876</v>
       </c>
       <c r="I78" t="n">
-        <v>4.776526791993009</v>
+        <v>4.805216976449875</v>
       </c>
       <c r="J78" t="n">
         <v>-14</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.190000057220459</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I81" t="n">
-        <v>4.931506720464348</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J81" t="n">
         <v>-14</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>88.80000305175781</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="I82" t="n">
-        <v>2.319819740095405</v>
+        <v>2.335600987842274</v>
       </c>
       <c r="J82" t="n">
         <v>-14</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.40999984741211</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="I83" t="n">
-        <v>4.866969548516588</v>
+        <v>4.873294238264276</v>
       </c>
       <c r="J83" t="n">
         <v>-14</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.46000003814697</v>
+        <v>14.17000007629395</v>
       </c>
       <c r="I84" t="n">
-        <v>2.074688791207255</v>
+        <v>2.117148894740604</v>
       </c>
       <c r="J84" t="n">
         <v>-14</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>51.79999923706055</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="I85" t="n">
-        <v>1.640926665095129</v>
+        <v>1.647286870417835</v>
       </c>
       <c r="J85" t="n">
         <v>-14</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.58000183105469</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="I86" t="n">
-        <v>2.388982451535764</v>
+        <v>2.414772674933939</v>
       </c>
       <c r="J86" t="n">
         <v>-14</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>66.87999725341797</v>
+        <v>66.94000244140625</v>
       </c>
       <c r="I87" t="n">
-        <v>1.943779984132045</v>
+        <v>1.942037574823683</v>
       </c>
       <c r="J87" t="n">
         <v>-14</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.039999961853027</v>
+        <v>7.059999942779541</v>
       </c>
       <c r="I88" t="n">
-        <v>8.522727318908558</v>
+        <v>8.498583638285107</v>
       </c>
       <c r="J88" t="n">
         <v>-14</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>7.25</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I89" t="n">
-        <v>6.482758620689655</v>
+        <v>6.35135126949837</v>
       </c>
       <c r="J89" t="n">
         <v>-14</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.20000076293945</v>
+        <v>23.34000015258789</v>
       </c>
       <c r="I91" t="n">
-        <v>4.310344685839137</v>
+        <v>4.284490117662326</v>
       </c>
       <c r="J91" t="n">
         <v>-14</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.840000152587891</v>
+        <v>4.769999980926514</v>
       </c>
       <c r="I92" t="n">
-        <v>4.442148620285518</v>
+        <v>4.507337544228646</v>
       </c>
       <c r="J92" t="n">
         <v>-14</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>22.7450008392334</v>
+        <v>23.02000045776367</v>
       </c>
       <c r="I93" t="n">
-        <v>1.18707403841582</v>
+        <v>1.172893113079589</v>
       </c>
       <c r="J93" t="n">
         <v>-14</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.680000305175781</v>
+        <v>9.659999847412109</v>
       </c>
       <c r="I94" t="n">
-        <v>2.066115637342102</v>
+        <v>2.07039340744482</v>
       </c>
       <c r="J94" t="n">
         <v>-14</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.824999809265137</v>
+        <v>8.725000381469727</v>
       </c>
       <c r="I95" t="n">
-        <v>2.719546800987239</v>
+        <v>2.750716212112899</v>
       </c>
       <c r="J95" t="n">
         <v>-14</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>20.79999923706055</v>
+        <v>20.69000053405762</v>
       </c>
       <c r="I96" t="n">
-        <v>3.79807706238956</v>
+        <v>3.818269596946546</v>
       </c>
       <c r="J96" t="n">
         <v>-14</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.320000171661377</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="I97" t="n">
-        <v>1.748120244344976</v>
+        <v>1.768060759567112</v>
       </c>
       <c r="J97" t="n">
         <v>-14</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>35.40000152587891</v>
+        <v>34.5</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9887005223548793</v>
+        <v>1.014492753623188</v>
       </c>
       <c r="J99" t="n">
         <v>-14</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.684999942779541</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="I100" t="n">
-        <v>8.291697901937885</v>
+        <v>8.373111927224565</v>
       </c>
       <c r="J100" t="n">
         <v>-14</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.279999971389771</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I101" t="n">
-        <v>2.631578980390385</v>
+        <v>2.643171828376432</v>
       </c>
       <c r="J101" t="n">
         <v>-14</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.14999961853027</v>
+        <v>12.75</v>
       </c>
       <c r="I102" t="n">
-        <v>1.52091259164883</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="J102" t="n">
         <v>-14</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.474999904632568</v>
+        <v>7.34499979019165</v>
       </c>
       <c r="I103" t="n">
-        <v>1.377926438984522</v>
+        <v>1.402314539716446</v>
       </c>
       <c r="J103" t="n">
         <v>-14</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.769000053405762</v>
+        <v>5.693999767303467</v>
       </c>
       <c r="I104" t="n">
-        <v>3.293465041447389</v>
+        <v>3.336845938966013</v>
       </c>
       <c r="J104" t="n">
         <v>-14</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.03999996185303</v>
+        <v>9.920000076293945</v>
       </c>
       <c r="I105" t="n">
-        <v>4.302788860969957</v>
+        <v>4.354838676184695</v>
       </c>
       <c r="J105" t="n">
         <v>-14</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>25.21999931335449</v>
+        <v>25.32999992370605</v>
       </c>
       <c r="I106" t="n">
-        <v>1.744647152972012</v>
+        <v>1.737070672425107</v>
       </c>
       <c r="J106" t="n">
         <v>-14</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.25</v>
+        <v>7.170000076293945</v>
       </c>
       <c r="I108" t="n">
-        <v>6.482758620689655</v>
+        <v>6.555090585758197</v>
       </c>
       <c r="J108" t="n">
         <v>-14</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>56.29999923706055</v>
+        <v>54.81999969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>2.486678541690678</v>
+        <v>2.553812491414843</v>
       </c>
       <c r="J109" t="n">
         <v>-14</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.460999965667725</v>
+        <v>3.49399995803833</v>
       </c>
       <c r="I110" t="n">
-        <v>8.668015110543969</v>
+        <v>8.586147784856639</v>
       </c>
       <c r="J110" t="n">
         <v>-14</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.5</v>
+        <v>15.75</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J111" t="n">
         <v>-14</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.440000057220459</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="I112" t="n">
-        <v>4.941860382914093</v>
+        <v>4.871060158609155</v>
       </c>
       <c r="J112" t="n">
         <v>-14</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>23</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>3.043478260869565</v>
+        <v>3.090507778319433</v>
       </c>
       <c r="J113" t="n">
         <v>-14</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.420000076293945</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I114" t="n">
-        <v>1.446280946139471</v>
+        <v>1.458333275384376</v>
       </c>
       <c r="J114" t="n">
         <v>-14</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.579999923706055</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I115" t="n">
-        <v>5.913978575484007</v>
+        <v>5.935251859643496</v>
       </c>
       <c r="J115" t="n">
         <v>-14</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>51.15000152587891</v>
+        <v>51.09999847412109</v>
       </c>
       <c r="I117" t="n">
-        <v>1.388074249891824</v>
+        <v>1.389432526812246</v>
       </c>
       <c r="J117" t="n">
         <v>-14</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>107.4000015258789</v>
+        <v>108.3000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.256983222364952</v>
+        <v>1.246537360996028</v>
       </c>
       <c r="J118" t="n">
         <v>-14</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.239999771118164</v>
+        <v>7.360000133514404</v>
       </c>
       <c r="I119" t="n">
-        <v>1.104972410622668</v>
+        <v>1.086956502021148</v>
       </c>
       <c r="J119" t="n">
         <v>-14</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I120" t="n">
-        <v>1.136363636363636</v>
+        <v>1.162790697674419</v>
       </c>
       <c r="J120" t="n">
         <v>-14</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.224999904632568</v>
+        <v>4.234000205993652</v>
       </c>
       <c r="I121" t="n">
-        <v>4.023668729876202</v>
+        <v>4.015115534461901</v>
       </c>
       <c r="J121" t="n">
         <v>-14</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>56.29999923706055</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="I123" t="n">
-        <v>0.799289531257718</v>
+        <v>0.800711732902232</v>
       </c>
       <c r="J123" t="n">
         <v>-14</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.880000114440918</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6802720956035777</v>
+        <v>0.6944444168497026</v>
       </c>
       <c r="J124" t="n">
         <v>-14</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>36.70000076293945</v>
+        <v>36.22000122070312</v>
       </c>
       <c r="I125" t="n">
-        <v>2.861035362866573</v>
+        <v>2.898950758178955</v>
       </c>
       <c r="J125" t="n">
         <v>-14</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.81999969482422</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="I127" t="n">
-        <v>2.132435502287748</v>
+        <v>2.124091743792214</v>
       </c>
       <c r="J127" t="n">
         <v>-14</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.3799991607666</v>
+        <v>26.93000030517578</v>
       </c>
       <c r="I128" t="n">
-        <v>2.274450413525199</v>
+        <v>2.227998489419563</v>
       </c>
       <c r="J128" t="n">
         <v>-14</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>36.84999847412109</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9497965115135539</v>
+        <v>0.9358288388245591</v>
       </c>
       <c r="J129" t="n">
         <v>-14</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.160000085830688</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5379746689320455</v>
+        <v>0.5312499920837582</v>
       </c>
       <c r="J130" t="n">
         <v>-14</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.890000104904175</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3460207486854598</v>
+        <v>0.3484320696428174</v>
       </c>
       <c r="J131" t="n">
         <v>-14</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>21.04999923706055</v>
+        <v>21.1299991607666</v>
       </c>
       <c r="I132" t="n">
-        <v>5.320665275978407</v>
+        <v>5.300520797367444</v>
       </c>
       <c r="J132" t="n">
         <v>-14</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.279999732971191</v>
+        <v>8.920000076293945</v>
       </c>
       <c r="I134" t="n">
-        <v>2.801724218549686</v>
+        <v>2.914798181347371</v>
       </c>
       <c r="J134" t="n">
         <v>-14</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.23799991607666</v>
+        <v>2.227999925613403</v>
       </c>
       <c r="I135" t="n">
-        <v>4.124218206487116</v>
+        <v>4.142729043161362</v>
       </c>
       <c r="J135" t="n">
         <v>-14</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.159999847412109</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I136" t="n">
-        <v>3.820960762339775</v>
+        <v>3.829321519180174</v>
       </c>
       <c r="J136" t="n">
         <v>-21</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5.199999809265137</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I137" t="n">
-        <v>1.846153913870368</v>
+        <v>1.777777746381093</v>
       </c>
       <c r="J137" t="n">
         <v>-21</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.25</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="I138" t="n">
-        <v>4.8</v>
+        <v>4.72440951977241</v>
       </c>
       <c r="J138" t="n">
         <v>-21</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.100000381469727</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J140" t="n">
         <v>-21</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.86000061035156</v>
+        <v>18.8799991607666</v>
       </c>
       <c r="I141" t="n">
-        <v>2.651113381860488</v>
+        <v>2.648305202465369</v>
       </c>
       <c r="J141" t="n">
         <v>-21</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.47999954223633</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I143" t="n">
-        <v>3.229974255721245</v>
+        <v>3.259452379572819</v>
       </c>
       <c r="J143" t="n">
         <v>-21</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.210000038146973</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="I145" t="n">
-        <v>3.426791236535292</v>
+        <v>3.405572735307695</v>
       </c>
       <c r="J145" t="n">
         <v>-21</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.289999961853027</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I151" t="n">
-        <v>3.017832663253934</v>
+        <v>3.076923035882762</v>
       </c>
       <c r="J151" t="n">
         <v>-21</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>24.64999961853027</v>
+        <v>24.29999923706055</v>
       </c>
       <c r="I152" t="n">
-        <v>2.474645068722197</v>
+        <v>2.510288144658348</v>
       </c>
       <c r="J152" t="n">
         <v>-28</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>2.799999952316284</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I153" t="n">
-        <v>5.357142948374458</v>
+        <v>5.395683508766814</v>
       </c>
       <c r="J153" t="n">
         <v>-28</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9.210000038146973</v>
+        <v>9.130000114440918</v>
       </c>
       <c r="I155" t="n">
-        <v>5.542888142079868</v>
+        <v>5.591456665948364</v>
       </c>
       <c r="J155" t="n">
         <v>-28</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>7.014999866485596</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I156" t="n">
-        <v>3.848895297773765</v>
+        <v>3.7815126757544</v>
       </c>
       <c r="J156" t="n">
         <v>-28</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>7.090000152587891</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="I157" t="n">
-        <v>4.936530218158711</v>
+        <v>4.950494929305689</v>
       </c>
       <c r="J157" t="n">
         <v>-28</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>42.79999923706055</v>
+        <v>43.59999847412109</v>
       </c>
       <c r="I158" t="n">
-        <v>2.570093503757611</v>
+        <v>2.522935868112262</v>
       </c>
       <c r="J158" t="n">
         <v>-28</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>17</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I159" t="n">
-        <v>4.411764705882353</v>
+        <v>4.385964814437848</v>
       </c>
       <c r="J159" t="n">
         <v>-28</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>11.30000019073486</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I160" t="n">
-        <v>3.805309670282723</v>
+        <v>3.771929950778691</v>
       </c>
       <c r="J160" t="n">
         <v>-28</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>4.519999980926514</v>
+        <v>4.414999961853027</v>
       </c>
       <c r="I161" t="n">
-        <v>3.318584084800214</v>
+        <v>3.397508523126764</v>
       </c>
       <c r="J161" t="n">
         <v>-28</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>12.03999996185303</v>
+        <v>11.84000015258789</v>
       </c>
       <c r="I162" t="n">
-        <v>1.637616284258314</v>
+        <v>1.665278694754952</v>
       </c>
       <c r="J162" t="n">
         <v>-28</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>28.5</v>
+        <v>27.95000076293945</v>
       </c>
       <c r="I163" t="n">
-        <v>3.859649122807018</v>
+        <v>3.93559917700809</v>
       </c>
       <c r="J163" t="n">
         <v>-28</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>68.59999847412109</v>
+        <v>68.09999847412109</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6851312105747415</v>
+        <v>0.6901615426299991</v>
       </c>
       <c r="J164" t="n">
         <v>-28</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>89</v>
+        <v>88.69999694824219</v>
       </c>
       <c r="I165" t="n">
-        <v>1.348314606741573</v>
+        <v>1.35287490562172</v>
       </c>
       <c r="J165" t="n">
         <v>-28</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>22.5</v>
+        <v>22.45000076293945</v>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1.202672564919094</v>
       </c>
       <c r="J166" t="n">
         <v>-28</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>10.35000038146973</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I167" t="n">
-        <v>3.671497449220761</v>
+        <v>3.653846287868437</v>
       </c>
       <c r="J167" t="n">
         <v>-28</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>34.75</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8633093525179856</v>
+        <v>0.8583690799747171</v>
       </c>
       <c r="J168" t="n">
         <v>-28</v>
@@ -10296,112 +10296,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cube Labs S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vivenda Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>